--- a/question1/results/result1.xlsx
+++ b/question1/results/result1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结果汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="结果汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="口径说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/question1/results/result1.xlsx
+++ b/question1/results/result1.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B2" s="10" t="n">
-        <v>1406.6411</v>
+        <v>1407.047708333333</v>
       </c>
     </row>
     <row r="3" ht="14" customHeight="1">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B3" s="10" t="n">
-        <v>1406.329866666666</v>
+        <v>1406.485483333333</v>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>1407.38385</v>
+        <v>1406.856858333333</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>1409.07395</v>
+        <v>1408.2289</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>1409.80455</v>
+        <v>1409.43925</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>576.6400166666666</v>
+        <v>909.88895</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>577.8597</v>
+        <v>577.2498583333332</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>577.9938666666667</v>
+        <v>577.9267833333333</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>911.1613833333333</v>
+        <v>577.9109583333334</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>580.41545</v>
+        <v>579.1217499999999</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>582.5140166666666</v>
+        <v>581.4647333333332</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>583.0740499999999</v>
+        <v>582.7940333333333</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>584.2049166666666</v>
+        <v>583.6394833333334</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>585.4397833333333</v>
+        <v>584.8223499999999</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>586.1447499999999</v>
+        <v>585.7922666666666</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>586.3207666666666</v>
+        <v>586.2327583333333</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>586.4253</v>
+        <v>586.3730333333333</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>586.8496</v>
+        <v>586.6374499999999</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>587.8210166666667</v>
+        <v>587.3353083333333</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>589.5475666666666</v>
+        <v>588.6842916666667</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>590.8134666666666</v>
+        <v>590.1805166666666</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>590.2131166666666</v>
+        <v>590.5132916666666</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>591.0662666666666</v>
+        <v>590.6396916666665</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>593.3678333333332</v>
+        <v>592.21705</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>593.6596833333333</v>
+        <v>593.5137583333333</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>592.7863833333333</v>
+        <v>593.2230333333333</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>593.3378666666666</v>
+        <v>593.0621249999999</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>596.6757666666666</v>
+        <v>595.0068166666666</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>597.78025</v>
+        <v>597.2280083333333</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>595.1624999999999</v>
+        <v>596.471375</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>590.6065</v>
+        <v>592.8845</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>589.4851833333333</v>
+        <v>590.0458416666667</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>578.4554499999999</v>
+        <v>583.9703166666666</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>1383.659783333333</v>
+        <v>1397.724283333333</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>591.1401999999999</v>
+        <v>570.7333249999999</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="B68" s="10" t="n">
-        <v>575.1709166666665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="B69" s="10" t="n">
-        <v>0</v>
+        <v>556.0307743827168</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>179.2771713991827</v>
+        <v>546.5221083333333</v>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B72" s="10" t="n">
-        <v>520.1245166666665</v>
+        <v>532.0781916666664</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B73" s="10" t="n">
-        <v>486.4028999999999</v>
+        <v>503.2637083333332</v>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B74" s="10" t="n">
-        <v>480.4124499999999</v>
+        <v>483.4076749999998</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>485.3</v>
+        <v>482.856225</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="B76" s="10" t="n">
-        <v>488.6069666666666</v>
+        <v>486.9534833333335</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="B77" s="10" t="n">
-        <v>498.2707333333332</v>
+        <v>493.43885</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="B91" s="10" t="n">
-        <v>112.0898666666667</v>
+        <v>89.70494166666663</v>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="B92" s="10" t="n">
-        <v>266.7326936213991</v>
+        <v>194.0571031893023</v>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="B93" s="10" t="n">
-        <v>197.5235166666666</v>
+        <v>175.8926833333335</v>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B94" s="10" t="n">
-        <v>244.8140333333332</v>
+        <v>221.1687749999998</v>
       </c>
     </row>
     <row r="95" ht="14" customHeight="1">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="B95" s="10" t="n">
-        <v>295.5346166666667</v>
+        <v>270.174325</v>
       </c>
     </row>
     <row r="96" ht="14" customHeight="1">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B96" s="10" t="n">
-        <v>345.7775000000001</v>
+        <v>320.6560583333335</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="B97" s="10" t="n">
-        <v>394.9314833333333</v>
+        <v>370.3544916666667</v>
       </c>
     </row>
     <row r="98" ht="14" customHeight="1">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="B98" s="10" t="n">
-        <v>445.4316500000001</v>
+        <v>420.1815666666669</v>
       </c>
     </row>
     <row r="99" ht="14" customHeight="1">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="B99" s="10" t="n">
-        <v>495.6965833333333</v>
+        <v>470.5641166666666</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B100" s="10" t="n">
-        <v>547.11905</v>
+        <v>521.4078166666666</v>
       </c>
     </row>
     <row r="101" ht="14" customHeight="1">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B101" s="10" t="n">
-        <v>599.9854333333333</v>
+        <v>573.5522416666668</v>
       </c>
     </row>
     <row r="102" ht="14" customHeight="1">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="B102" s="10" t="n">
-        <v>635.4297499999999</v>
+        <v>617.7075916666665</v>
       </c>
     </row>
     <row r="103" ht="14" customHeight="1">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="B103" s="10" t="n">
-        <v>660.8306833333334</v>
+        <v>648.1302166666667</v>
       </c>
     </row>
     <row r="104" ht="14" customHeight="1">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="B104" s="10" t="n">
-        <v>702.0369333333333</v>
+        <v>681.4338083333332</v>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B105" s="10" t="n">
-        <v>738.0657833333333</v>
+        <v>720.0513583333333</v>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B106" s="10" t="n">
-        <v>775.9447166666666</v>
+        <v>757.0052499999999</v>
       </c>
     </row>
     <row r="107" ht="14" customHeight="1">
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="B107" s="10" t="n">
-        <v>826.08325</v>
+        <v>801.0139833333333</v>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1">
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B108" s="10" t="n">
-        <v>762.4227999999999</v>
+        <v>794.253025</v>
       </c>
     </row>
     <row r="109" ht="14" customHeight="1">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B109" s="10" t="n">
-        <v>636.9826166666667</v>
+        <v>699.7027083333332</v>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="B110" s="10" t="n">
-        <v>531.8940499999999</v>
+        <v>639.0719583333334</v>
       </c>
     </row>
     <row r="111" ht="14" customHeight="1">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B111" s="10" t="n">
-        <v>678.8305333333333</v>
+        <v>659.9959166666665</v>
       </c>
     </row>
     <row r="112" ht="14" customHeight="1">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B112" s="10" t="n">
-        <v>686.2684999999999</v>
+        <v>682.5495166666667</v>
       </c>
     </row>
     <row r="113" ht="14" customHeight="1">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="B113" s="10" t="n">
-        <v>696.5043833333333</v>
+        <v>691.3864416666665</v>
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="B114" s="10" t="n">
-        <v>0</v>
+        <v>596.9193999999995</v>
       </c>
     </row>
     <row r="115" ht="14" customHeight="1">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B126" s="10" t="n">
-        <v>715.8689166666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" ht="14" customHeight="1">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="B127" s="10" t="n">
-        <v>717.0051166666667</v>
+        <v>716.4370166666668</v>
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="B128" s="10" t="n">
-        <v>720.1603</v>
+        <v>718.5827083333334</v>
       </c>
     </row>
     <row r="129" ht="14" customHeight="1">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B129" s="10" t="n">
-        <v>717.0548666666666</v>
+        <v>718.6075833333334</v>
       </c>
     </row>
     <row r="130" ht="14" customHeight="1">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B130" s="10" t="n">
-        <v>720.4459666666667</v>
+        <v>718.7504166666668</v>
       </c>
     </row>
     <row r="131" ht="14" customHeight="1">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B131" s="10" t="n">
-        <v>738.1347166666666</v>
+        <v>729.2903416666666</v>
       </c>
     </row>
     <row r="132" ht="14" customHeight="1">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B132" s="10" t="n">
-        <v>671.6935666666666</v>
+        <v>704.9141416666666</v>
       </c>
     </row>
     <row r="133" ht="14" customHeight="1">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="B133" s="10" t="n">
-        <v>1393.790316666667</v>
+        <v>616.0752749999999</v>
       </c>
     </row>
     <row r="134" ht="14" customHeight="1">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="B134" s="10" t="n">
-        <v>1384.8989</v>
+        <v>1389.344608333333</v>
       </c>
     </row>
     <row r="135" ht="14" customHeight="1">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="B135" s="10" t="n">
-        <v>568.8260499999999</v>
+        <v>1393.529141666666</v>
       </c>
     </row>
     <row r="136" ht="14" customHeight="1">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B136" s="10" t="n">
-        <v>1396.98855</v>
+        <v>566.2406333333333</v>
       </c>
     </row>
     <row r="137" ht="14" customHeight="1">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B137" s="10" t="n">
-        <v>1397.759866666667</v>
+        <v>1397.374208333333</v>
       </c>
     </row>
     <row r="138" ht="14" customHeight="1">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="B138" s="10" t="n">
-        <v>566.7474333333332</v>
+        <v>1398.920316666667</v>
       </c>
     </row>
     <row r="139" ht="14" customHeight="1">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="B139" s="10" t="n">
-        <v>1399.873766666667</v>
+        <v>899.9772666666665</v>
       </c>
     </row>
     <row r="140" ht="14" customHeight="1">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B140" s="10" t="n">
-        <v>567.83015</v>
+        <v>567.1852916666667</v>
       </c>
     </row>
     <row r="141" ht="14" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="B141" s="10" t="n">
-        <v>569.3586333333333</v>
+        <v>568.5943916666666</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="B142" s="10" t="n">
-        <v>1403.663516666667</v>
+        <v>1403.177741666667</v>
       </c>
     </row>
     <row r="143" ht="14" customHeight="1">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="B143" s="10" t="n">
-        <v>904.9487166666665</v>
+        <v>1404.306116666667</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="B144" s="10" t="n">
-        <v>573.1768333333333</v>
+        <v>572.3961083333334</v>
       </c>
     </row>
     <row r="145" ht="14" customHeight="1">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="B145" s="10" t="n">
-        <v>574.1209833333332</v>
+        <v>573.6489083333333</v>
       </c>
     </row>
   </sheetData>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>4499.999999999999</v>
+        <v>4500</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>833.3333333333333</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>6365.8412</v>
+        <v>6452.200574999999</v>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>4787.964288065848</v>
+        <v>4982.706316049384</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>1702.996983333333</v>
+        <v>1903.495675</v>
       </c>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>5286.035176954731</v>
+        <v>5393.849311522635</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>91.1013833333335</v>
+        <v>49.31380833333344</v>
       </c>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>5780.131883333333</v>
+        <v>5066.474908333334</v>
       </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
@@ -2092,7 +2092,7 @@
         <v>5333.333333333332</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2859.868116666667</v>
+        <v>3573.525091666666</v>
       </c>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>59482.69899835391</v>
+        <v>59540.18466923868</v>
       </c>
     </row>
     <row r="3">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>35126.94858928963</v>
+        <v>35205.88556237151</v>
       </c>
     </row>
     <row r="4">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>48052.04659084666</v>
+        <v>48004.76141820083</v>
       </c>
     </row>
     <row r="5">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>0.2689812176287015</v>
+        <v>0.2666167996197284</v>
       </c>
     </row>
     <row r="6">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20740.66613168725</v>
+        <v>21043.22229423868</v>
       </c>
     </row>
     <row r="7">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>16799.93956666667</v>
+        <v>17045.01005833333</v>
       </c>
     </row>
     <row r="8">
@@ -2219,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2241,94 +2241,106 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>时间对应</t>
+          <t>数据预处理</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>附件00:10对应00:00-00:10；输出副本修正原模板偏移，源文件未修改。</t>
+          <t>附件数据视为瞬时端点值；00:00复制24:00数值，每个10分钟区间取两端点算术平均。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>供电路径</t>
+          <t>时间对应</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>外网和光伏可直接供负载，也可充电；容量只约束当时电池储电。</t>
+          <t>区间平均数据依次对应00:00-00:10至23:50-24:00；源附件未修改。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>效率</t>
+          <t>供电路径</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>主解释为充电、放电各90%；充放电量为微网侧电量。</t>
+          <t>外网和光伏可直接供负载，也可充电；容量只约束当时电池储电。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>储能约束</t>
+          <t>效率</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>额定12000kWh，运行范围1200至10800kWh，日初日末均6000kWh。</t>
+          <t>主解释为充电、放电各90%；充放电量为微网侧电量。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>功率约束</t>
+          <t>储能约束</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>充放电各不超过5000kW，即每10分钟各不超过833.3333kWh。</t>
+          <t>额定12000kWh，运行范围1200至10800kWh，日初日末均6000kWh。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>弃光约束</t>
+          <t>功率约束</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>严格按截图：0≤r≤GΔt，仅允许弃光；没有已购电弃用变量，不售电。</t>
+          <t>充放电各不超过5000kW，即每10分钟各不超过833.3333kWh。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>求解模型</t>
+          <t>弃光约束</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>纯购电费用目标的MILP；u为二元开关；没有额外平局成本或附加放电负载上限。</t>
+          <t>严格按截图：0≤r≤GΔt，仅允许弃光；没有已购电弃用变量，不售电。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
+          <t>求解模型</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>纯购电费用目标的MILP；u为二元开关；没有额外平局成本或附加放电负载上限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
           <t>显示精度</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>电量显示4位小数、费用2位小数；底层数值不截断，总计直接保存数值。</t>
         </is>
